--- a/data/support/analysis_table/model_metrics_comparison.xlsx
+++ b/data/support/analysis_table/model_metrics_comparison.xlsx
@@ -463,13 +463,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8259</v>
+        <v>0.826</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8236</v>
+        <v>0.824</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7037</v>
+        <v>0.704</v>
       </c>
       <c r="E2" t="n">
         <v>0.822</v>
@@ -482,16 +482,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7786</v>
+        <v>0.779</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7661</v>
+        <v>0.766</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6207</v>
+        <v>0.621</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7612</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="4">
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8888</v>
+        <v>0.889</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8892</v>
+        <v>0.889</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6949</v>
+        <v>0.695</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8864</v>
+        <v>0.886</v>
       </c>
     </row>
     <row r="5">
@@ -520,16 +520,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9492</v>
+        <v>0.949</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9496</v>
+        <v>0.95</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8371</v>
+        <v>0.837</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9486</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8652</v>
+        <v>0.865</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8662</v>
+        <v>0.866</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6727</v>
+        <v>0.673</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8636</v>
+        <v>0.864</v>
       </c>
     </row>
     <row r="7">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8789</v>
+        <v>0.879</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8789</v>
+        <v>0.879</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7968</v>
+        <v>0.797</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8783</v>
+        <v>0.878</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7847</v>
+        <v>0.785</v>
       </c>
       <c r="C8" t="n">
         <v>0.777</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6252</v>
+        <v>0.625</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7735</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="9">
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1192</v>
+        <v>0.119</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1204</v>
+        <v>0.12</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1963</v>
+        <v>0.196</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1229</v>
+        <v>0.123</v>
       </c>
     </row>
     <row r="10">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3733</v>
+        <v>0.373</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3772</v>
+        <v>0.377</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5766</v>
+        <v>0.577</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3852</v>
+        <v>0.385</v>
       </c>
     </row>
   </sheetData>
@@ -676,22 +676,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>*0.8259*</t>
+          <t>*0.826*</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.8236</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.7037</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.8220</t>
+          <t>0.822</t>
         </is>
       </c>
     </row>
@@ -703,22 +703,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>*0.7786*</t>
+          <t>*0.779*</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7661</t>
+          <t>0.766</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6207</t>
+          <t>0.621</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7612</t>
+          <t>0.761</t>
         </is>
       </c>
     </row>
@@ -730,22 +730,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.8888</t>
+          <t>*0.889*</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>*0.8892*</t>
+          <t>*0.889*</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6949</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.8864</t>
+          <t>0.886</t>
         </is>
       </c>
     </row>
@@ -757,22 +757,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.9492</t>
+          <t>0.949</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>*0.9496*</t>
+          <t>*0.950*</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.8371</t>
+          <t>0.837</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.9486</t>
+          <t>0.949</t>
         </is>
       </c>
     </row>
@@ -784,22 +784,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.8652</t>
+          <t>0.865</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>*0.8662*</t>
+          <t>*0.866*</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.6727</t>
+          <t>0.673</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.8636</t>
+          <t>0.864</t>
         </is>
       </c>
     </row>
@@ -811,22 +811,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>*0.8789*</t>
+          <t>*0.879*</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>*0.8789*</t>
+          <t>*0.879*</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.7968</t>
+          <t>0.797</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.8783</t>
+          <t>0.878</t>
         </is>
       </c>
     </row>
@@ -838,22 +838,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>*0.7847*</t>
+          <t>*0.785*</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.7770</t>
+          <t>0.777</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.6252</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.7735</t>
+          <t>0.773</t>
         </is>
       </c>
     </row>
@@ -865,22 +865,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>*0.1192*</t>
+          <t>*0.119*</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.120</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.1963</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.1229</t>
+          <t>0.123</t>
         </is>
       </c>
     </row>
@@ -892,22 +892,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>*0.3733*</t>
+          <t>*0.373*</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.3772</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.5766</t>
+          <t>0.577</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3852</t>
+          <t>0.385</t>
         </is>
       </c>
     </row>
